--- a/programme/chair-sheets/S01.xlsx
+++ b/programme/chair-sheets/S01.xlsx
@@ -52,13 +52,13 @@
     <t xml:space="preserve">Co-chair</t>
   </si>
   <si>
-    <t xml:space="preserve">-</t>
+    <t xml:space="preserve">D. Geetha</t>
   </si>
   <si>
     <t xml:space="preserve">Joining link</t>
   </si>
   <si>
-    <t xml:space="preserve">to be confirmed</t>
+    <t xml:space="preserve">https://meet.google.com/pqz-zpbv-htc</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
